--- a/backend/data/uploads/MES/2026-07-01_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-01_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F14FA44-91CB-4FD3-A0F0-ABD1761AB41F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{290EDA08-19B3-4AA8-865D-0BFB769D0AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{4D9CCD0E-46A2-4DFF-A145-260339671C5C}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{3FCCAD99-95A3-4606-B1BC-A16D52DB9937}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4AD41D5-8870-47D7-933F-BBABE7CA093E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{888DA9E5-E28A-46E9-B6C4-22FF5565769B}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-01_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-01_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{290EDA08-19B3-4AA8-865D-0BFB769D0AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A45247B-7C9D-4576-8A0B-08CE2766B9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{3FCCAD99-95A3-4606-B1BC-A16D52DB9937}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{DE1AE470-63DE-40D3-B441-7FADAF543E77}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{888DA9E5-E28A-46E9-B6C4-22FF5565769B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D223FE73-B4BB-4D1F-8E6F-F8D3F673C44B}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-01_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-01_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A45247B-7C9D-4576-8A0B-08CE2766B9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{939EAF9D-BA88-4677-8AAE-80C710C9DBDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{DE1AE470-63DE-40D3-B441-7FADAF543E77}"/>
+    <workbookView xWindow="-30240" yWindow="8376" windowWidth="23040" windowHeight="12012" xr2:uid="{88825B68-C0CF-4458-BE6A-4567FA7E8408}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D223FE73-B4BB-4D1F-8E6F-F8D3F673C44B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7314E42-9F63-47B6-9831-1C8BAF164DBB}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
